--- a/INSTANCES/instances_xlsx/A_MTN_3/136FL_5A_1.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_3/136FL_5A_1.xlsx
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4981,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
